--- a/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_64942_completo.xlsx
+++ b/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_64942_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd79fc31bec1b4f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R131223d5fcdf4ae2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,7 +255,172 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">

--- a/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_64942_completo.xlsx
+++ b/137552_Cuenca_Mala/_raw_reportes_xlsx/IDConfig_64942_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R131223d5fcdf4ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R91f525ae5ef944bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1074,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8101</x:v>
+        <x:v>      3.2880</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0478</x:v>
+        <x:v>      3.2880</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9464</x:v>
+        <x:v>      3.4307</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1940</x:v>
+        <x:v>      3.5270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.3345</x:v>
+        <x:v>      3.5757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.2755</x:v>
+        <x:v>      3.9740</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3360</x:v>
+        <x:v>      4.2836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3124</x:v>
+        <x:v>      4.2836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2062</x:v>
+        <x:v>      4.1797</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5331</x:v>
+        <x:v>      4.2836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3018</x:v>
+        <x:v>      4.2836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3633</x:v>
+        <x:v>      4.3897</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5681</x:v>
+        <x:v>      4.4958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5186</x:v>
+        <x:v>      4.4958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.7509</x:v>
+        <x:v>      4.7143</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0784</x:v>
+        <x:v>      4.9328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3134</x:v>
+        <x:v>      4.4979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8367</x:v>
+        <x:v>      4.9328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9063</x:v>
+        <x:v>      4.9328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9714</x:v>
+        <x:v>      5.1577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1023</x:v>
+        <x:v>      5.1577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1097</x:v>
+        <x:v>      5.1577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1395</x:v>
+        <x:v>      5.1577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.3680</x:v>
+        <x:v>      5.3867</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.5818</x:v>
+        <x:v>      5.5033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.8088</x:v>
+        <x:v>      5.8571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.8382</x:v>
+        <x:v>      5.8571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1093</x:v>
+        <x:v>      6.1057</x:v>
       </x:c>
     </x:row>
     <x:row>
